--- a/Assets/Excel/DialogueTable.xlsx
+++ b/Assets/Excel/DialogueTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kjghk\OneDrive\Desktop\mindsneakers\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85647133-2800-427C-81AC-974A8CEAAADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892FBBD8-9835-4040-984E-56E51116C72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DoubleDialogue" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="25">
   <si>
     <t>Hero_Normal</t>
   </si>
@@ -94,6 +94,18 @@
   </si>
   <si>
     <t>Image</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text6</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -549,7 +561,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -575,7 +587,7 @@
         <v>12</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -601,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/DialogueTable.xlsx
+++ b/Assets/Excel/DialogueTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kjghk\OneDrive\Desktop\mindsneakers\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892FBBD8-9835-4040-984E-56E51116C72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5AC9E5-FAE7-49E6-AC2A-CDEFE0EBC83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="70">
   <si>
     <t>Hero_Normal</t>
   </si>
@@ -47,16 +47,10 @@
     <t>Context</t>
   </si>
   <si>
-    <t>Demon_Normal</t>
-  </si>
-  <si>
     <t>Left</t>
   </si>
   <si>
     <t>Hero_Angry</t>
-  </si>
-  <si>
-    <t>Demon_Laugh</t>
   </si>
   <si>
     <t>Right</t>
@@ -69,10 +63,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Text1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -97,15 +87,1514 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Text4</t>
+    <t>None</t>
+  </si>
+  <si>
+    <t>늦은 저녁, 노을이 다 지고 어둑어둑해질 즈음,</t>
+  </si>
+  <si>
+    <t>주인공</t>
+  </si>
+  <si>
+    <t>스테이시</t>
+  </si>
+  <si>
+    <t>Stacy_Gown_Gloomy</t>
+  </si>
+  <si>
+    <t>도착했다….</t>
+  </si>
+  <si>
+    <t>돌아오신 걸 환영해요. 오늘 정말 힘드셨나 보네요. 어느 정도의 **휴식-*이 필요해 보입니다. 사용자님의 저녁을 준비해드릴까요?</t>
+  </si>
+  <si>
+    <t>Stacy_Gown_Default</t>
+  </si>
+  <si>
+    <t>죄송합니다. 사용자님의 불편을 초래했네요. 사용자님의 분노는 정말 ** 정당 -* 합니다.</t>
+  </si>
+  <si>
+    <t>Stacy_Gown_Angry</t>
+  </si>
+  <si>
+    <t>으으으….. 사용자 피드백을 잘 수용하는 모델이라더니 진짜!</t>
+  </si>
+  <si>
+    <t>저녁이나 준비해 줘.</t>
+  </si>
+  <si>
+    <t>스테이시는 그리고 자기 방으로 돌아갔다.</t>
+  </si>
+  <si>
+    <t>생각을 되찾기 전까지는 몰랐지만, ‘악마 표준 대화집’으로 나오는 말들은 내가 듣기에도 화가 나긴 한다.</t>
+  </si>
+  <si>
+    <t>바로 초콜릿.</t>
+  </si>
+  <si>
+    <t>그녀가 어떤 정신 상태이든 진정시켜주는 만병통치약 같은 거다.</t>
+  </si>
+  <si>
+    <t>저번에 효과를 확인한 이후로 항상 준비해두고 있다.</t>
+  </si>
+  <si>
+    <t>요리를 시작하자. 항상 느끼지만 사물인터넷 포트에 연결하는 느낌은 항상 질색이다.</t>
+  </si>
+  <si>
+    <t>‘사용자님</t>
+  </si>
+  <si>
+    <t>그리고 조금의 부스럭거리는 소리 후, 스테이시가 내려왔다</t>
+  </si>
+  <si>
+    <t>Stacy_Pajama_Default</t>
+  </si>
+  <si>
+    <t>*스테이시 스탠딩 일러스트(잠옷) 표시</t>
+  </si>
+  <si>
+    <t>표준 탄수화물 블럭과 배양고기 볶음입니다. 사용자님의 영양상태와 예산을 고려해 준비했어요.</t>
+  </si>
+  <si>
+    <t>또? 생활비 상한을 좀 늘려야 하나….</t>
+  </si>
+  <si>
+    <t>스테이시는 앉아서 배양고기 볶음과 함께 표준 탄수화물 블럭을 같이 먹으며 조잘조잘 말을 시작한다.</t>
+  </si>
+  <si>
+    <t>Stacy_Pajama_Angry</t>
+  </si>
+  <si>
+    <t>연구라곤 하나도 모르는 사람들이 행정직에 있으니까 연구자들이 죽어 나가지!</t>
+  </si>
+  <si>
+    <t>그렇군요, 정말 힘드셨겠어요. 연구자들의 고충은 참 어렵네요. 사용자님의 분노는 정말 **정당-*해요.</t>
+  </si>
+  <si>
+    <t>Stacy_Pajama_Explosion</t>
+  </si>
+  <si>
+    <t>으아아아악!!</t>
+  </si>
+  <si>
+    <t>Stacy_Pajama_Gloomy</t>
+  </si>
+  <si>
+    <t>내가 대화할 사람 한 명이 없어서 가정용 악마랑 이런 대화를 하고 있네 정신이 어떻게 되어 먹은 건지 진짜 그냥 다 때려칠까</t>
+  </si>
+  <si>
+    <t>불편함을 초래해 죄송합니다. 혹시 구체적으로 어떤 부분을 고치고 싶은지 알려주시면, 그 부분에 대해 오류 보고서를 작성하거나, 아니면 당장 적용할 수 있는 수정사항을 만들어 보겠습니다.</t>
+  </si>
+  <si>
+    <t>끼야아아악!!!</t>
+  </si>
+  <si>
+    <t>사용자님의 기분을 고려해 후식을 준비했습니다. 드셔보시겠습니까?</t>
+  </si>
+  <si>
+    <t>초콜릿?</t>
+  </si>
+  <si>
+    <t>스테이시가 행복한 표정으로 초콜릿을 먹기 시작한다.</t>
+  </si>
+  <si>
+    <t>Stacy_Pajama_Joy</t>
+  </si>
+  <si>
+    <t>그래도 사용자 피드백이 적용되고는 있는 건가? 내가 초콜릿 좋아하는 건 기억하고 있네.</t>
+  </si>
+  <si>
+    <t>그렇게 저녁식사가 끝나고, 스테이시는 방으로 돌아가서 다시 PC를 켜고 자리를 잡았다.</t>
+  </si>
+  <si>
+    <t>아무리 초콜릿이 만병통치약이라고 해도, 저 꼬장을 듣지 않기 위해서라도 무언가 조치는 필요해 보인다.</t>
+  </si>
+  <si>
+    <t>None</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Text5</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배고파</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죽는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알았네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메뉴는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Text6</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연구가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뭐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하루아침에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>끝나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아닌데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작자들은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맨날</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연구성과연구성과연구성과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거리고…</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대화로는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스테이시를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어떻게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>음식으로는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>충분히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가능하다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말투</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어떻게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이슈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때문인지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최근</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스테이시가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ‘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>악마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대화집’</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때문에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>횟수가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잦아지고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>끼익 (문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노이즈)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ‘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>핵심을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찌르셨어요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">’ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대사를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>웃기기까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(주방으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전환)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사운드</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -113,7 +1602,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -173,6 +1662,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -422,21 +1918,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="165.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -460,56 +1956,56 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>1001</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>1002</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
+      <c r="C3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -519,101 +2015,959 @@
       <c r="B4">
         <v>1003</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>14</v>
+      <c r="C4" t="s">
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
       </c>
       <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1004</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
         <v>8</v>
       </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1005</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="6" t="s">
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1002</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
       <c r="H6" s="6" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>1006</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1007</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>1008</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>1009</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>1010</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>1011</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>1012</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14">
         <v>2</v>
       </c>
-      <c r="B7">
-        <v>1003</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="B14">
+        <v>1013</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" t="s">
         <v>8</v>
       </c>
-      <c r="G7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>24</v>
+      <c r="H14" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>1014</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>1015</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1016</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>1017</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>1018</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>1019</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>1020</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>1021</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>1022</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>1023</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>1024</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>1025</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>1026</v>
+      </c>
+      <c r="C27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>1027</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>1028</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>1029</v>
+      </c>
+      <c r="C30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>1030</v>
+      </c>
+      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32">
+        <v>1031</v>
+      </c>
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2</v>
+      </c>
+      <c r="B33">
+        <v>1032</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="B34">
+        <v>1033</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" t="s">
+        <v>8</v>
+      </c>
+      <c r="H34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2</v>
+      </c>
+      <c r="B35">
+        <v>1034</v>
+      </c>
+      <c r="C35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" t="s">
+        <v>39</v>
+      </c>
+      <c r="G35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2</v>
+      </c>
+      <c r="B36">
+        <v>1035</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2</v>
+      </c>
+      <c r="B37">
+        <v>1036</v>
+      </c>
+      <c r="C37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" t="s">
+        <v>56</v>
+      </c>
+      <c r="G37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2</v>
+      </c>
+      <c r="B38">
+        <v>1037</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H38" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>2</v>
+      </c>
+      <c r="B39">
+        <v>1038</v>
+      </c>
+      <c r="C39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" t="s">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" t="s">
+        <v>8</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2</v>
+      </c>
+      <c r="B40">
+        <v>1039</v>
+      </c>
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G40" t="s">
+        <v>8</v>
+      </c>
+      <c r="H40" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -635,16 +2989,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -658,13 +3012,13 @@
         <v>1001</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -675,13 +3029,13 @@
         <v>1002</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -692,13 +3046,13 @@
         <v>1003</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.45">
@@ -709,13 +3063,13 @@
         <v>1001</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -726,13 +3080,13 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -743,13 +3097,13 @@
         <v>1003</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/DialogueTable.xlsx
+++ b/Assets/Excel/DialogueTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kjghk\OneDrive\Desktop\mindsneakers\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5AC9E5-FAE7-49E6-AC2A-CDEFE0EBC83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A602356D-5300-4320-B87E-41275C6E2FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>1001</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3">
         <v>1002</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4">
         <v>1003</v>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5">
         <v>1004</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6">
         <v>1005</v>
@@ -2088,7 +2088,7 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>1006</v>
@@ -2114,7 +2114,7 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>1007</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9">
         <v>1008</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10">
         <v>1009</v>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11">
         <v>1010</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12">
         <v>1011</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13">
         <v>1012</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14">
         <v>1013</v>
@@ -2296,7 +2296,7 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15">
         <v>1014</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16">
         <v>1015</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17">
         <v>1016</v>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18">
         <v>1017</v>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19">
         <v>1018</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20">
         <v>1019</v>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21">
         <v>1020</v>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22">
         <v>1021</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23">
         <v>1022</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24">
         <v>1023</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25">
         <v>1024</v>
@@ -2582,7 +2582,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26">
         <v>1025</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27">
         <v>1026</v>
@@ -2634,7 +2634,7 @@
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28">
         <v>1027</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29">
         <v>1028</v>
@@ -2686,7 +2686,7 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30">
         <v>1029</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31">
         <v>1030</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32">
         <v>1031</v>
@@ -2764,7 +2764,7 @@
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33">
         <v>1032</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34">
         <v>1033</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35">
         <v>1034</v>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36">
         <v>1035</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37">
         <v>1036</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38">
         <v>1037</v>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39">
         <v>1038</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40">
         <v>1039</v>
